--- a/quizzes/015_ordinal_numbers_knowledge_survey--quizzes.xlsx
+++ b/quizzes/015_ordinal_numbers_knowledge_survey--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_page_1</t>
+          <t>first_question</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>What is the first number in the sequence?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>second_question</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>What is the second number in the sequence?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>third_question</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>What is the third number in the sequence?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>survey_page_2</t>
+          <t>fourth_question</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>What is the fourth number in the sequence?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>fifth_question</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>What is the fifth number in the sequence?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>sixth_question</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>What is the sixth number in the sequence?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,92 +653,92 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>seventh_question</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>What is the seventh number in the sequence?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>eighth_question</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>What is the eighth number in the sequence?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fourth_question</t>
+          <t>ninth_question</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fourth_question</t>
+          <t>What is the ninth number in the sequence?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>survey_page_3</t>
+          <t>tenth_question</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fifth_question</t>
+          <t>What is the tenth number in the sequence?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sixth_question</t>
+          <t>first_position</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sixth_question</t>
+          <t>Which of the following numbers is in first position in the sequence?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>seventh_question</t>
+          <t>second_position</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seventh_question</t>
+          <t>Which of the following numbers is in second position in the sequence?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eighth_question</t>
+          <t>third_position</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>eighth_question</t>
+          <t>Which of the following numbers is in third position in the sequence?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ninth_question</t>
+          <t>fourth_position</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ninth_question</t>
+          <t>Which of the following numbers is in fourth position in the sequence?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tenth_question</t>
+          <t>fifth_position</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tenth_question</t>
+          <t>Which of the following numbers is in fifth position in the sequence?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eleventh_question</t>
+          <t>sixth_position</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>eleventh_question</t>
+          <t>Which of the following numbers is in sixth position in the sequence?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>twelfth_question</t>
+          <t>seventh_position</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>twelfth_question</t>
+          <t>Which of the following numbers is in seventh position in the sequence?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>thirteenth_question</t>
+          <t>eighth_position</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>thirteenth_question</t>
+          <t>Which of the following numbers is in eighth position in the sequence?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>fourteenth_question</t>
+          <t>ninth_position</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fourteenth_question</t>
+          <t>Which of the following numbers is in ninth position in the sequence?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fifteenth_question</t>
+          <t>tenth_position</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fifteenth_question</t>
+          <t>Which of the following numbers is in tenth position in the sequence?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sixteenth_question</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sixteenth_question</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>seventeenth_question</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>seventeenth_question</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>eighteenth_question</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>eighteenth_question</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nineteenth_question</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>nineteenth_question</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>twentieth_question</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>twentieth_question</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,10 +983,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1296,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1198,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1215,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1232,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1249,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1300,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1317,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1334,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>second_question_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1351,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1368,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1385,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1436,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1453,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1470,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1487,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1504,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>third_question_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1521,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1538,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1555,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1572,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1589,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1606,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1623,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1640,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1657,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1674,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>fourth_question_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1691,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1708,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1725,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1742,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1759,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1776,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1793,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1810,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1827,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1844,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>fifth_question_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1861,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1878,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +1895,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +1912,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +1929,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +1946,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +1963,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2095,7 +1980,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +1997,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,7 +2014,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>sixth_question_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2146,7 +2031,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2163,7 +2048,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2065,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2197,7 +2082,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,7 +2099,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,7 +2116,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2248,7 +2133,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2265,7 +2150,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2167,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2299,7 +2184,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sixth_question_choices</t>
+          <t>seventh_question_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2201,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,7 +2218,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2350,7 +2235,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2367,7 +2252,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2384,7 +2269,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2401,7 +2286,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2418,7 +2303,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2435,7 +2320,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2452,7 +2337,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2469,7 +2354,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ninth_question_choices</t>
+          <t>eighth_question_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2486,7 +2371,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2503,7 +2388,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2520,7 +2405,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2537,7 +2422,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2554,7 +2439,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2571,7 +2456,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2588,7 +2473,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2605,7 +2490,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2622,7 +2507,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2639,7 +2524,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>eleventh_question_choices</t>
+          <t>ninth_question_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2656,7 +2541,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2673,7 +2558,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2690,7 +2575,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2707,7 +2592,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2724,7 +2609,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2741,7 +2626,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2758,7 +2643,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2775,7 +2660,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2792,7 +2677,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2809,7 +2694,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>thirteenth_question_choices</t>
+          <t>tenth_question_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2826,7 +2711,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2843,7 +2728,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2860,7 +2745,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2877,7 +2762,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2894,7 +2779,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2911,7 +2796,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2928,7 +2813,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2945,7 +2830,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2962,7 +2847,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2979,7 +2864,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sixteenth_question_choices</t>
+          <t>first_position_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2988,6 +2873,1536 @@
         </is>
       </c>
       <c r="C111" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>second_position_choices</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>third_position_choices</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>fourth_position_choices</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>fifth_position_choices</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>sixth_position_choices</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>seventh_position_choices</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>eighth_position_choices</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ninth_position_choices</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tenth_position_choices</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
